--- a/mis-portal/reports/2026-06-08/IWS_20260608.xlsx
+++ b/mis-portal/reports/2026-06-08/IWS_20260608.xlsx
@@ -18,8 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="DD-MMM-YYYY"/>
+    <numFmt numFmtId="165" formatCode="₹#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,12 +51,16 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +80,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F7FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -111,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -122,11 +140,44 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -598,134 +649,468 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MF — Debt / Liquid Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Savings Fund - Growth</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>1708371.1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1722024.68</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1722024.6801</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1716743.33</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>5281.35</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>16657.45</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>13653.58</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>0.009768000000000001</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>0.007992000000000001</v>
+      </c>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Kotak Banking and PSU Debt Fund - Growth (Regular Plan)</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>43803</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>4219729.01</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>6397562.13</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>6397562.1336</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>6361093.56</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>36468.57</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>63242.13</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>2177833.12</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>0.009984</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>0.516107</v>
+      </c>
+      <c r="L6" s="12" t="n">
+        <v>0.06600500000000001</v>
+      </c>
+      <c r="M6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Total MF Debt / Liquid</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>SUM(C5:C6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>SUM(D5:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
+        <f>SUM(E5:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="15">
+        <f>SUM(F5:F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="15">
+        <f>SUM(G5:G6)</f>
+        <v/>
+      </c>
+      <c r="H7" s="15">
+        <f>SUM(H5:H6)</f>
+        <v/>
+      </c>
+      <c r="I7" s="15">
+        <f>SUM(I5:I6)</f>
+        <v/>
+      </c>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>A. TOTAL FIXED INCOME</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>MF — Equity Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>HDFC BSE Sensex Index Fund - Regular Plan</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>44299</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3525513.25</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>3525513.2497</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>3549366.25</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-23853</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>58795.68</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>425513.25</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.01696</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0.137262</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.025277</v>
+      </c>
+      <c r="M12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Dynamic Asset Allocation Active FOF-Growth (formerly ICICI Prudential Advisor Series</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>43711</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>14674999.74</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>28052133.59</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>28052133.5856</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>28171669.81</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>-119536.22</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>1374388.39</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>13377133.85</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.05151799999999999</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>0.911559</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>0.100551</v>
+      </c>
+      <c r="M13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Multi-Asset Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>44827</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>576325</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>833110.28</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>833110.2751</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>838746.24</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-5635.96</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>27821.58</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>256785.28</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.034549</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>0.445556</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.104512</v>
+      </c>
+      <c r="M14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Multi-Asset Fund - Growth</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>659151.22</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>659151.2181000001</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>663688.16</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>-4536.94</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>21292.85</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>159151.22</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0.033382</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>0.318302</v>
+      </c>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Total MF — Equity Funds</t>
+        </is>
+      </c>
+      <c r="C16" s="15">
+        <f>SUM(C12:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>SUM(D12:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
+        <f>SUM(E12:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="15">
+        <f>SUM(F12:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="15">
+        <f>SUM(G12:G15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="15">
+        <f>SUM(H12:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="15">
+        <f>SUM(I12:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>B. TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>ALTERNATES</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>D. TOTAL ALTERNATES</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>E. Funds in Transit</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>F. Broker Balance</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>G. Funds in Bank</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>H. GRAND TOTAL (A+B+D+E+F+G)</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Report generated on 08 Jun 2026 10:06 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="n"/>
+      <c r="K28" s="16" t="n"/>
+      <c r="L28" s="16" t="n"/>
+      <c r="M28" s="16" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Report generated on 08 Jun 2026 11:25 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A14:M14"/>
+  <mergeCells count="16">
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A24:M24"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A4:M4"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
